--- a/SuppXLS/Scen_SYS_FossilFuel_Update.xlsx
+++ b/SuppXLS/Scen_SYS_FossilFuel_Update.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\times-ireland-model\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A9105C-A1CA-4B94-BA75-1A5CC69D1F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FDE6AAA-01F8-4D96-B64D-F2735CDA3627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -69,6 +66,9 @@
   </si>
   <si>
     <t>IMPELC*,IMPBIO*</t>
+  </si>
+  <si>
+    <t>*2</t>
   </si>
 </sst>
 </file>
@@ -164,111 +164,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Cover"/>
-      <sheetName val="Regions"/>
-      <sheetName val="config"/>
-      <sheetName val="FF2price"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="3">
-          <cell r="B3">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6" t="str">
-            <v>Case #</v>
-          </cell>
-          <cell r="I6" t="str">
-            <v>FF_price</v>
-          </cell>
-          <cell r="J6" t="str">
-            <v>ELC, BIO</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>1</v>
-          </cell>
-          <cell r="I7">
-            <v>1.2</v>
-          </cell>
-          <cell r="J7">
-            <v>1.1499999999999999</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="H8">
-            <v>2</v>
-          </cell>
-          <cell r="I8">
-            <v>1.3</v>
-          </cell>
-          <cell r="J8">
-            <v>1.2250000000000001</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="H9">
-            <v>3</v>
-          </cell>
-          <cell r="I9">
-            <v>1.4</v>
-          </cell>
-          <cell r="J9">
-            <v>1.2999999999999998</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="H10">
-            <v>4</v>
-          </cell>
-          <cell r="I10">
-            <v>1.5</v>
-          </cell>
-          <cell r="J10">
-            <v>1.375</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="H11">
-            <v>5</v>
-          </cell>
-          <cell r="I11">
-            <v>1.6</v>
-          </cell>
-          <cell r="J11">
-            <v>1.4500000000000002</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="H12">
-            <v>6</v>
-          </cell>
-          <cell r="I12">
-            <v>2</v>
-          </cell>
-          <cell r="J12">
-            <v>1.75</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -567,9 +462,8 @@
       <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="str">
-        <f>"*"&amp;VLOOKUP([1]config!$B$3,[1]config!$H$6:$I$12,2,FALSE)</f>
-        <v>*1.5</v>
+      <c r="E4" t="s">
+        <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>8</v>
@@ -579,9 +473,8 @@
       <c r="D5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" t="str">
-        <f>"*"&amp;VLOOKUP([1]config!$B$3,[1]config!$H$6:$J$12,3,FALSE)</f>
-        <v>*1.375</v>
+      <c r="E5" t="s">
+        <v>10</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>9</v>
